--- a/SGC-CKN/Excel/a5e45c08-41b9-4901-a161-b6d6f590b90d_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-165_D800_01-04-2026.xlsx
+++ b/SGC-CKN/Excel/a5e45c08-41b9-4901-a161-b6d6f590b90d_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-165_D800_01-04-2026.xlsx
@@ -162,7 +162,7 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">08:52
+    <t xml:space="preserve">08:32
 01/04/2026</t>
   </si>
   <si>
@@ -1358,13 +1358,13 @@
         <v>-38.75</v>
       </c>
       <c r="H17" s="25">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="I17" s="25">
         <v>13.13</v>
       </c>
       <c r="J17" s="12">
-        <v>6.11</v>
+        <v>7.23</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>29</v>
@@ -1393,13 +1393,13 @@
         <v>-43.95</v>
       </c>
       <c r="H18" s="28">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="I18" s="28">
         <v>5.2</v>
       </c>
       <c r="J18" s="8">
-        <v>2.86</v>
+        <v>2.42</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>29</v>
@@ -1734,13 +1734,13 @@
         <v>-38.75</v>
       </c>
       <c r="G8" s="25">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="H8" s="25">
         <v>13.13</v>
       </c>
       <c r="I8" s="12">
-        <v>6.11</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1763,13 +1763,13 @@
         <v>-43.95</v>
       </c>
       <c r="G9" s="28">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="H9" s="28">
         <v>5.2</v>
       </c>
       <c r="I9" s="8">
-        <v>2.86</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
